--- a/404/404.xlsx
+++ b/404/404.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="18540" windowHeight="6495" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Problem 01" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Problem 02" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Problem 03" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Problem 04" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Problem 01" sheetId="1" r:id="rId1"/>
+    <sheet name="Problem 02" sheetId="2" r:id="rId2"/>
+    <sheet name="Problem 03" sheetId="3" r:id="rId3"/>
+    <sheet name="Problem 04" sheetId="4" r:id="rId4"/>
+    <sheet name="Problm 05" sheetId="5" r:id="rId5"/>
+    <sheet name="Problem 06" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
@@ -19,35 +22,35 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{29AD88FE-D6EB-44A2-8CAB-2CA16F135489}" keepAlive="1" name="Query - Table001 (Page 1)" description="Connection to the 'Table001 (Page 1)' query in the workbook." type="5" background="1" refreshedVersion="0">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" keepAlive="1" name="Query - Table001 (Page 1)" description="Connection to the 'Table001 (Page 1)' query in the workbook." type="5" refreshedVersion="0" background="1">
     <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=&quot;Table001 (Page 1)&quot;;Extended Properties=&quot;&quot;" command="SELECT * FROM [Table001 (Page 1)]"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
-  <si>
-    <t xml:space="preserve">Income Class (taka)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of household</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under 500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income (X)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of households having income &gt;=X (Y)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log Y</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="163">
+  <si>
+    <t>Income Class (taka)</t>
+  </si>
+  <si>
+    <t>Percentage of household</t>
+  </si>
+  <si>
+    <t>Under 500</t>
+  </si>
+  <si>
+    <t>Income (X)</t>
+  </si>
+  <si>
+    <t>% of households having income &gt;=X (Y)</t>
+  </si>
+  <si>
+    <t>log X</t>
+  </si>
+  <si>
+    <t>log Y</t>
   </si>
   <si>
     <t>500-999</t>
@@ -80,22 +83,22 @@
     <t>15000-24999</t>
   </si>
   <si>
-    <t xml:space="preserve">25000 or over</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b0 hat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b1 hat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A hat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gama hat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rho hat</t>
+    <t>25000 or over</t>
+  </si>
+  <si>
+    <t>b0 hat</t>
+  </si>
+  <si>
+    <t>b1 hat</t>
+  </si>
+  <si>
+    <t>A hat</t>
+  </si>
+  <si>
+    <t>gama hat</t>
+  </si>
+  <si>
+    <t>rho hat</t>
   </si>
   <si>
     <t>LL</t>
@@ -104,10 +107,10 @@
     <t>UL</t>
   </si>
   <si>
-    <t xml:space="preserve">Mid value (Xi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">freq (fi)</t>
+    <t>Mid value (Xi)</t>
+  </si>
+  <si>
+    <t>freq (fi)</t>
   </si>
   <si>
     <t>fixi</t>
@@ -119,16 +122,16 @@
     <t>fi(Xi-Xbar)^2</t>
   </si>
   <si>
-    <t xml:space="preserve">In of class upper boundary (yi)</t>
+    <t>In of class upper boundary (yi)</t>
   </si>
   <si>
     <t>zi</t>
   </si>
   <si>
-    <t xml:space="preserve">phi (z)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d phi(z)</t>
+    <t>phi (z)</t>
+  </si>
+  <si>
+    <t>d phi(z)</t>
   </si>
   <si>
     <t>Ei</t>
@@ -143,7 +146,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve">CHI SQ</t>
+    <t>CHI SQ</t>
   </si>
   <si>
     <t>N</t>
@@ -152,70 +155,70 @@
     <t>Tab</t>
   </si>
   <si>
-    <t xml:space="preserve">X bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S^2 bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S^2 + Xbar ^2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mu hat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma^2 hat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma hat</t>
+    <t>X bar</t>
+  </si>
+  <si>
+    <t>S^2 bar</t>
+  </si>
+  <si>
+    <t>S^2 + Xbar ^2</t>
+  </si>
+  <si>
+    <t>mu hat</t>
+  </si>
+  <si>
+    <t>sigma^2 hat</t>
+  </si>
+  <si>
+    <t>sigma hat</t>
   </si>
   <si>
     <t>Income</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Persons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative Persons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative Income (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative Persons (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumilative mid value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumilative mid %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No of workers A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumilative Frequency A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumilative Frequency A (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No of workers B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumilative Frequency B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumilative Frequency B (%)</t>
+    <t>Number of Persons</t>
+  </si>
+  <si>
+    <t>Cumulative Income</t>
+  </si>
+  <si>
+    <t>Cumulative Persons</t>
+  </si>
+  <si>
+    <t>Cumulative Income (%)</t>
+  </si>
+  <si>
+    <t>Cumulative Persons (%)</t>
+  </si>
+  <si>
+    <t>Daily Income</t>
+  </si>
+  <si>
+    <t>Mid value</t>
+  </si>
+  <si>
+    <t>Cumilative mid value</t>
+  </si>
+  <si>
+    <t>Cumilative mid %</t>
+  </si>
+  <si>
+    <t>No of workers A</t>
+  </si>
+  <si>
+    <t>Cumilative Frequency A</t>
+  </si>
+  <si>
+    <t>Cumilative Frequency A (%)</t>
+  </si>
+  <si>
+    <t>No of workers B</t>
+  </si>
+  <si>
+    <t>Cumilative Frequency B</t>
+  </si>
+  <si>
+    <t>Cumilative Frequency B (%)</t>
   </si>
   <si>
     <t>0−100</t>
@@ -233,10 +236,10 @@
     <t>400−500</t>
   </si>
   <si>
-    <t xml:space="preserve">Cumulative Population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Area Under Curve</t>
+    <t>Cumulative Population</t>
+  </si>
+  <si>
+    <t>Area Under Curve</t>
   </si>
   <si>
     <t>A+B</t>
@@ -257,10 +260,10 @@
     <t>Efi</t>
   </si>
   <si>
-    <t xml:space="preserve">Xi = ln (E0i)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yi = ln(Efi)</t>
+    <t>Xi = ln (E0i)</t>
+  </si>
+  <si>
+    <t>Yi = ln(Efi)</t>
   </si>
   <si>
     <t>Sums</t>
@@ -287,55 +290,324 @@
     <t>niXi^2</t>
   </si>
   <si>
-    <t xml:space="preserve">Var (b)</t>
+    <t>Var (b)</t>
   </si>
   <si>
     <t>niXiYi</t>
   </si>
   <si>
-    <t xml:space="preserve">SE b</t>
+    <t>SE b</t>
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>years</t>
+  </si>
+  <si>
+    <t>GCF</t>
+  </si>
+  <si>
+    <t>1965-66</t>
+  </si>
+  <si>
+    <t>1966-67</t>
+  </si>
+  <si>
+    <t>1967-68</t>
+  </si>
+  <si>
+    <t>1968-69</t>
+  </si>
+  <si>
+    <t>1969-70</t>
+  </si>
+  <si>
+    <t>1970-71</t>
+  </si>
+  <si>
+    <t>1971-72</t>
+  </si>
+  <si>
+    <t>1972-73</t>
+  </si>
+  <si>
+    <t>1973-74</t>
+  </si>
+  <si>
+    <t>1974-75</t>
+  </si>
+  <si>
+    <t>1975-76</t>
+  </si>
+  <si>
+    <t>1976-77</t>
+  </si>
+  <si>
+    <t>1977-78</t>
+  </si>
+  <si>
+    <t>1978-79</t>
+  </si>
+  <si>
+    <t>1979-80</t>
+  </si>
+  <si>
+    <t>1980-81</t>
+  </si>
+  <si>
+    <t>1981-82</t>
+  </si>
+  <si>
+    <t>Semi-avg</t>
+  </si>
+  <si>
+    <t>2y moving avg</t>
+  </si>
+  <si>
+    <t>CMA</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>Coded Year</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Y hat</t>
+  </si>
+  <si>
+    <t>Binary</t>
+  </si>
+  <si>
+    <t>Avg</t>
+  </si>
+  <si>
+    <t>Counting Runs</t>
+  </si>
+  <si>
+    <t>n0</t>
+  </si>
+  <si>
+    <t>n1</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>LN Q</t>
+  </si>
+  <si>
+    <t>LN L</t>
+  </si>
+  <si>
+    <t>LN K</t>
+  </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+  <si>
+    <t>a0</t>
+  </si>
+  <si>
+    <t>b1</t>
+  </si>
+  <si>
+    <t>b2</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>r</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -350,33 +622,114 @@
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="34">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -395,12 +748,12 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -409,12 +762,8 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr bwMode="auto">
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -454,10 +803,7 @@
           <c:tx>
             <c:v>Curve</c:v>
           </c:tx>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
@@ -469,10 +815,7 @@
           <c:marker>
             <c:symbol val="circle"/>
             <c:size val="5"/>
-            <c:spPr bwMode="auto">
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -546,10 +889,7 @@
           <c:tx>
             <c:v>Standard</c:v>
           </c:tx>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
@@ -561,10 +901,7 @@
           <c:marker>
             <c:symbol val="circle"/>
             <c:size val="5"/>
-            <c:spPr bwMode="auto">
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -633,30 +970,26 @@
           <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLeaderLines val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
         </c:dLbls>
-        <c:axId val="803675647"/>
-        <c:axId val="803677311"/>
+        <c:axId val="11056256"/>
+        <c:axId val="11058560"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="803675647"/>
+        <c:axId val="11056256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="100.000000"/>
+          <c:max val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -673,10 +1006,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr bwMode="auto">
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -709,23 +1039,20 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="803677311"/>
+        <c:crossAx val="11058560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="803677311"/>
+        <c:axId val="11058560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="100.000000"/>
+          <c:max val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -742,10 +1069,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr bwMode="auto">
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -778,14 +1102,11 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="803675647"/>
+        <c:crossAx val="11056256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:spPr bwMode="auto">
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -795,12 +1116,8 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr bwMode="auto">
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -832,14 +1149,7 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0">
-      <a:off x="0" y="0"/>
-      <a:ext cx="0" cy="0"/>
-    </a:xfrm>
-    <a:prstGeom prst="rect">
-      <a:avLst/>
-    </a:prstGeom>
+  <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
@@ -866,19 +1176,19 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -898,10 +1208,7 @@
           <c:tx>
             <c:v>Fact A</c:v>
           </c:tx>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
@@ -913,10 +1220,7 @@
           <c:marker>
             <c:symbol val="circle"/>
             <c:size val="5"/>
-            <c:spPr bwMode="auto">
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -990,10 +1294,7 @@
           <c:tx>
             <c:v>Fact B</c:v>
           </c:tx>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
@@ -1005,10 +1306,7 @@
           <c:marker>
             <c:symbol val="circle"/>
             <c:size val="5"/>
-            <c:spPr bwMode="auto">
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -1077,30 +1375,26 @@
           <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLeaderLines val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
         </c:dLbls>
-        <c:axId val="1077296719"/>
-        <c:axId val="1077298383"/>
+        <c:axId val="11287936"/>
+        <c:axId val="36445184"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1077296719"/>
+        <c:axId val="11287936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="100.000000"/>
+          <c:max val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -1117,10 +1411,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr bwMode="auto">
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -1153,23 +1444,20 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1077298383"/>
+        <c:crossAx val="36445184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1077298383"/>
+        <c:axId val="36445184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="100.000000"/>
+          <c:max val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -1186,10 +1474,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr bwMode="auto">
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -1222,14 +1507,11 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1077296719"/>
+        <c:crossAx val="11287936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:spPr bwMode="auto">
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -1239,12 +1521,8 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr bwMode="auto">
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -1276,14 +1554,7 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0">
-      <a:off x="0" y="0"/>
-      <a:ext cx="0" cy="0"/>
-    </a:xfrm>
-    <a:prstGeom prst="rect">
-      <a:avLst/>
-    </a:prstGeom>
+  <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
@@ -1310,19 +1581,19 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -1342,10 +1613,7 @@
           <c:tx>
             <c:v>Standard</c:v>
           </c:tx>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
@@ -1357,10 +1625,7 @@
           <c:marker>
             <c:symbol val="circle"/>
             <c:size val="5"/>
-            <c:spPr bwMode="auto">
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -1464,10 +1729,7 @@
           <c:tx>
             <c:v>Gini</c:v>
           </c:tx>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
@@ -1479,10 +1741,7 @@
           <c:marker>
             <c:symbol val="circle"/>
             <c:size val="5"/>
-            <c:spPr bwMode="auto">
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -1495,18 +1754,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:dLblPos val="r"/>
-            <c:showBubbleSize val="0"/>
-            <c:showCatName val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:showLegendKey val="0"/>
-            <c:showPercent val="0"/>
-            <c:showSerName val="0"/>
-            <c:showVal val="1"/>
-            <c:spPr bwMode="auto">
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
+            <c:spPr>
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
@@ -1535,6 +1783,14 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -1623,30 +1879,26 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLeaderLines val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
         </c:dLbls>
-        <c:axId val="1077335823"/>
-        <c:axId val="1077336239"/>
+        <c:axId val="36460032"/>
+        <c:axId val="36488320"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1077335823"/>
+        <c:axId val="36460032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="100.000000"/>
+          <c:max val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -1663,10 +1915,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr bwMode="auto">
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -1699,23 +1948,20 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1077336239"/>
+        <c:crossAx val="36488320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1077336239"/>
+        <c:axId val="36488320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="100.000000"/>
+          <c:max val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
-          <c:spPr bwMode="auto">
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -1732,10 +1978,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr bwMode="auto">
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -1768,14 +2011,11 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1077335823"/>
+        <c:crossAx val="36460032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:spPr bwMode="auto">
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -1787,14 +2027,7 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0">
-      <a:off x="7339011" y="14578011"/>
-      <a:ext cx="4571999" cy="2609849"/>
-    </a:xfrm>
-    <a:prstGeom prst="rect">
-      <a:avLst/>
-    </a:prstGeom>
+  <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
@@ -1821,7 +2054,769 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Problm 05'!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GCF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Problm 05'!$B$3:$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1965-66</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1966-67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1967-68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1968-69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1969-70</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1970-71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1971-72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1972-73</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1973-74</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1974-75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1975-76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1976-77</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1977-78</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1978-79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1979-80</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1980-81</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1981-82</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Problm 05'!$C$3:$C$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>22.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>21.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="39194624"/>
+        <c:axId val="39197312"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="39194624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="39197312"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="39197312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="15"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="39194624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Problm 05'!$D$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Semi-avg</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Problm 05'!$B$29:$B$45</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1965-66</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1966-67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1967-68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1968-69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1969-70</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1970-71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1971-72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1972-73</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1973-74</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1974-75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1975-76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1976-77</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1977-78</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1978-79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1979-80</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1980-81</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1981-82</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Problm 05'!$D$29:$D$45</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="4">
+                  <c:v>18.137499999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.325000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="132277760"/>
+        <c:axId val="132373504"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="132277760"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="132373504"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="132373504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="15"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="132277760"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Problm 05'!$C$74</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Problm 05'!$A$75:$A$91</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1965-66</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1966-67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1967-68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1968-69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1969-70</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1970-71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1971-72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1972-73</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1973-74</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1974-75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1975-76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1976-77</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1977-78</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1978-79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1979-80</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1980-81</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1981-82</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Problm 05'!$C$75:$C$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>22.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>21.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Problm 05'!$D$74</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y hat</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Problm 05'!$A$75:$A$91</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1965-66</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1966-67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1967-68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1968-69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1969-70</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1970-71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1971-72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1972-73</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1973-74</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1974-75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1975-76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1976-77</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1977-78</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1978-79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1979-80</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1980-81</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1981-82</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Problm 05'!$D$75:$D$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>17.649019607843137</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.862745098039216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.076470588235292</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.290196078431372</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.503921568627451</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.717647058823527</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.931372549019606</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19.145098039215686</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.358823529411762</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.572549019607841</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>19.786274509803921</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19.999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.213725490196076</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20.427450980392155</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20.641176470588231</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20.854901960784311</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>21.06862745098039</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="135363200"/>
+        <c:axId val="157224960"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="135363200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="157224960"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="157224960"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="15"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="135363200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -3676,8 +4671,8 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1238250</xdr:colOff>
@@ -3690,14 +4685,14 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm rot="0">
+      <xdr:xfrm>
         <a:off x="0" y="0"/>
         <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
@@ -3709,7 +4704,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1409699</xdr:colOff>
@@ -3722,14 +4717,14 @@
       <xdr:row>53</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm rot="0">
+      <xdr:xfrm>
         <a:off x="0" y="0"/>
         <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
@@ -3741,7 +4736,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1328736</xdr:colOff>
@@ -3754,16 +4749,16 @@
       <xdr:row>92</xdr:row>
       <xdr:rowOff>90486</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3"/>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm rot="0">
-        <a:off x="7339011" y="14578011"/>
-        <a:ext cx="4571999" cy="2609849"/>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3777,7 +4772,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
@@ -3799,7 +4794,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
@@ -3817,291 +4812,673 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>447260</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>77856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>115955</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>46382</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>91109</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>107676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>405847</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>24848</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Oval 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4381500" y="2277719"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>t</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>318053</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>102706</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19878</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19879</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Oval 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3995531" y="881271"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>p</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>72888</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>6628</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>387626</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>122583</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Oval 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4976192" y="1381541"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>p</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>498614</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>150746</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200439</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>67919</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Oval 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5401918" y="730529"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>p</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>435666</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>178908</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>137491</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>96081</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Oval 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5951883" y="1156256"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>p</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>223631</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>41418</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>538369</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>157374</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Oval 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6352761" y="621201"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>p</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>301487</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>69576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>3312</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>185532</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Oval 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5204791" y="2040837"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>t</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304801</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>72890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6626</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>188845</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Oval 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5821018" y="1845368"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>t</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>175593</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>26508</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>490331</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>142464</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Oval 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6304723" y="1600204"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>t</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>493646</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>96084</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>195471</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>13256</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Oval 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6622776" y="1272214"/>
+          <a:ext cx="314738" cy="314738"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>t</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="27" name="Chart 26"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="28" name="Chart 27"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4292,20 +5669,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:K24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="18.28515625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="23.5703125"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="10.5703125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="36"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -4313,7 +5692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>2</v>
       </c>
@@ -4333,12 +5712,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5">
-        <v>28.899999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="H5">
         <v>100</v>
@@ -4356,7 +5735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>8</v>
       </c>
@@ -4379,7 +5758,7 @@
         <v>1.9365137424788932</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>9</v>
       </c>
@@ -4402,12 +5781,12 @@
         <v>1.7596678446896303</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8">
-        <v>5.5999999999999996</v>
+        <v>5.6</v>
       </c>
       <c r="H8">
         <v>2000</v>
@@ -4425,12 +5804,12 @@
         <v>1.3979400086720375</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
         <v>3000</v>
@@ -4448,7 +5827,7 @@
         <v>1.1583624920952496</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -4471,7 +5850,7 @@
         <v>0.94448267215016835</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -4494,12 +5873,12 @@
         <v>0.75587485567249091</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12">
-        <v>0.69999999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="H12">
         <v>6000</v>
@@ -4517,12 +5896,12 @@
         <v>0.60205999132796173</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>15</v>
       </c>
       <c r="D13">
-        <v>0.80000000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="H13">
         <v>8000</v>
@@ -4540,7 +5919,7 @@
         <v>0.36172783601759168</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>16</v>
       </c>
@@ -4563,12 +5942,12 @@
         <v>0.20411998265592304</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>17</v>
       </c>
       <c r="D15">
-        <v>0.29999999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="H15">
         <v>15000</v>
@@ -4583,10 +5962,10 @@
       </c>
       <c r="K15">
         <f t="shared" si="1"/>
-        <v>-0.096910013008059889</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>-9.6910013008059889E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="H16">
         <v>25000</v>
       </c>
@@ -4603,7 +5982,7 @@
         <v>-0.52287874528034683</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
         <v>18</v>
       </c>
@@ -4612,7 +5991,7 @@
         <v>4.8366637466843834</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
         <v>19</v>
       </c>
@@ -4621,7 +6000,7 @@
         <v>-1.1309810157097999</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H22" t="s">
         <v>20</v>
       </c>
@@ -4630,7 +6009,7 @@
         <v>68653.668187228628</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H23" t="s">
         <v>21</v>
       </c>
@@ -4639,7 +6018,7 @@
         <v>1.1309810157097999</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
         <v>22</v>
       </c>
@@ -4649,22 +6028,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:O23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="13.42578125"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" width="28.140625"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30">
+    <row r="2" spans="3:15" ht="30" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
@@ -4705,7 +6083,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
       <c r="D3" s="4">
         <v>9</v>
@@ -4723,19 +6101,19 @@
         <v>36</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J14" si="3">LN(D3+0.5)</f>
+        <f t="shared" ref="J3:J14" si="0">LN(D3+0.5)</f>
         <v>2.2512917986064953</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K14" si="4">(J3-$F$21)/$F$23</f>
+        <f t="shared" ref="K3:K14" si="1">(J3-$F$21)/$F$23</f>
         <v>-3.2244343006250129</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L14" si="5">_xlfn.NORM.DIST(K3, 0, 1, 1)</f>
-        <v>0.00063110907690826896</v>
-      </c>
-    </row>
-    <row r="4">
+        <f t="shared" ref="L3:L14" si="2">_xlfn.NORM.DIST(K3, 0, 1, 1)</f>
+        <v>6.3110907690826896E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C4" s="5">
         <v>10</v>
       </c>
@@ -4743,50 +6121,50 @@
         <v>14</v>
       </c>
       <c r="E4" s="2">
-        <f t="shared" ref="E4:E14" si="6">(C4+D4)/2</f>
+        <f t="shared" ref="E4:E14" si="3">(C4+D4)/2</f>
         <v>12</v>
       </c>
       <c r="F4" s="5">
-        <v>3.2999999999999998</v>
+        <v>3.3</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G14" si="7">F4*E4</f>
+        <f t="shared" ref="G4:G14" si="4">F4*E4</f>
         <v>39.599999999999994</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H14" si="8">F4*E4*E4</f>
+        <f t="shared" ref="H4:H14" si="5">F4*E4*E4</f>
         <v>475.19999999999993</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I14" si="9">F4*(E4-$F$18)^2</f>
+        <f t="shared" ref="I4:I14" si="6">F4*(E4-$F$18)^2</f>
         <v>1653.665013825</v>
       </c>
       <c r="J4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>2.6741486494265287</v>
       </c>
       <c r="K4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>-2.1025228730238923</v>
       </c>
       <c r="L4">
-        <f t="shared" si="5"/>
-        <v>0.017753749082050244</v>
+        <f t="shared" si="2"/>
+        <v>1.7753749082050244E-2</v>
       </c>
       <c r="M4">
-        <f t="shared" ref="M4:M14" si="10">L4-L3</f>
-        <v>0.017122640005141975</v>
+        <f t="shared" ref="M4:M14" si="7">L4-L3</f>
+        <v>1.7122640005141975E-2</v>
       </c>
       <c r="N4">
-        <f t="shared" ref="N4:N14" si="11">$F$17*M4</f>
+        <f t="shared" ref="N4:N14" si="8">$F$17*M4</f>
         <v>1.7122640005141976</v>
       </c>
       <c r="O4">
-        <f t="shared" ref="O4:O14" si="12">(F4-N4)^2/N4</f>
+        <f t="shared" ref="O4:O14" si="9">(F4-N4)^2/N4</f>
         <v>1.4722645592654782</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C5" s="5">
         <v>15</v>
       </c>
@@ -4794,50 +6172,50 @@
         <v>19</v>
       </c>
       <c r="E5" s="2">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9.39</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="4"/>
+        <v>159.63</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="5"/>
+        <v>2713.71</v>
+      </c>
+      <c r="I5">
         <f t="shared" si="6"/>
-        <v>17</v>
-      </c>
-      <c r="F5" s="5">
-        <v>9.3900000000000006</v>
-      </c>
-      <c r="G5">
+        <v>2838.1801802475002</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>2.9704144655697009</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>-1.3164790757104154</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>9.400664845044622E-2</v>
+      </c>
+      <c r="M5">
         <f t="shared" si="7"/>
-        <v>159.63</v>
-      </c>
-      <c r="H5">
+        <v>7.6252899368395979E-2</v>
+      </c>
+      <c r="N5">
         <f t="shared" si="8"/>
-        <v>2713.71</v>
-      </c>
-      <c r="I5">
+        <v>7.6252899368395983</v>
+      </c>
+      <c r="O5">
         <f t="shared" si="9"/>
-        <v>2838.1801802475002</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="3"/>
-        <v>2.9704144655697009</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="4"/>
-        <v>-1.3164790757104154</v>
-      </c>
-      <c r="L5">
-        <f t="shared" si="5"/>
-        <v>0.09400664845044622</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="10"/>
-        <v>0.076252899368395979</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="11"/>
-        <v>7.6252899368395983</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="12"/>
         <v>0.40840435351502358</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C6" s="5">
         <v>20</v>
       </c>
@@ -4845,50 +6223,50 @@
         <v>24</v>
       </c>
       <c r="E6" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="F6" s="5">
         <v>13.08</v>
       </c>
       <c r="G6">
+        <f t="shared" si="4"/>
+        <v>287.76</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="5"/>
+        <v>6330.7199999999993</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="6"/>
+        <v>2006.47998207</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>3.1986731175506815</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>-0.71086989707308346</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>0.23858243086591838</v>
+      </c>
+      <c r="M6">
         <f t="shared" si="7"/>
-        <v>287.75999999999999</v>
-      </c>
-      <c r="H6">
+        <v>0.14457578241547214</v>
+      </c>
+      <c r="N6">
         <f t="shared" si="8"/>
-        <v>6330.7199999999993</v>
-      </c>
-      <c r="I6">
+        <v>14.457578241547214</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="9"/>
-        <v>2006.47998207</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="3"/>
-        <v>3.1986731175506815</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="4"/>
-        <v>-0.71086989707308346</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="5"/>
-        <v>0.23858243086591838</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="10"/>
-        <v>0.14457578241547214</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="11"/>
-        <v>14.457578241547214</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="12"/>
         <v>0.13126138969324538</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C7" s="5">
         <v>25</v>
       </c>
@@ -4896,50 +6274,50 @@
         <v>29</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="F7" s="5">
         <v>16.41</v>
       </c>
       <c r="G7">
+        <f t="shared" si="4"/>
+        <v>443.07</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="5"/>
+        <v>11962.89</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="6"/>
+        <v>895.09346420250006</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>3.3843902633457743</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>-0.2181305982656612</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>0.41366367870214205</v>
+      </c>
+      <c r="M7">
         <f t="shared" si="7"/>
-        <v>443.06999999999999</v>
-      </c>
-      <c r="H7">
+        <v>0.17508124783622367</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="8"/>
-        <v>11962.889999999999</v>
-      </c>
-      <c r="I7">
+        <v>17.508124783622367</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="9"/>
-        <v>895.09346420250006</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="3"/>
-        <v>3.3843902633457743</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="4"/>
-        <v>-0.2181305982656612</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="5"/>
-        <v>0.41366367870214205</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="10"/>
-        <v>0.17508124783622367</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="11"/>
-        <v>17.508124783622367</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="12"/>
-        <v>0.068875339609967029</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>6.8875339609967029E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C8" s="5">
         <v>30</v>
       </c>
@@ -4947,50 +6325,50 @@
         <v>34</v>
       </c>
       <c r="E8" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="F8" s="5">
+        <v>13.87</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="4"/>
+        <v>443.84</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="5"/>
+        <v>14202.88</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="6"/>
-        <v>32</v>
-      </c>
-      <c r="F8" s="5">
-        <v>13.869999999999999</v>
-      </c>
-      <c r="G8">
+        <v>78.92876416750002</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>3.5409593240373143</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>0.197273853756262</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>0.5781933805179621</v>
+      </c>
+      <c r="M8">
         <f t="shared" si="7"/>
-        <v>443.83999999999997</v>
-      </c>
-      <c r="H8">
+        <v>0.16452970181582005</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="8"/>
-        <v>14202.879999999999</v>
-      </c>
-      <c r="I8">
+        <v>16.452970181582003</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="9"/>
-        <v>78.92876416750002</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="3"/>
-        <v>3.5409593240373143</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="4"/>
-        <v>0.197273853756262</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="5"/>
-        <v>0.5781933805179621</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="10"/>
-        <v>0.16452970181582005</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="11"/>
-        <v>16.452970181582003</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="12"/>
         <v>0.40550337630893729</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C9" s="5">
         <v>35</v>
       </c>
@@ -4998,50 +6376,50 @@
         <v>39</v>
       </c>
       <c r="E9" s="2">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="F9" s="5">
+        <v>11.89</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="4"/>
+        <v>439.93</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="5"/>
+        <v>16277.41</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="6"/>
-        <v>37</v>
-      </c>
-      <c r="F9" s="5">
-        <v>11.890000000000001</v>
-      </c>
-      <c r="G9">
+        <v>81.275405872499974</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>3.6763006719070761</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>0.55635755905171536</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>0.71101677695527699</v>
+      </c>
+      <c r="M9">
         <f t="shared" si="7"/>
-        <v>439.93000000000001</v>
-      </c>
-      <c r="H9">
+        <v>0.13282339643731489</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="8"/>
-        <v>16277.41</v>
-      </c>
-      <c r="I9">
+        <v>13.28233964373149</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="9"/>
-        <v>81.275405872499974</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="3"/>
-        <v>3.6763006719070761</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="4"/>
-        <v>0.55635755905171536</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="5"/>
-        <v>0.71101677695527699</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="10"/>
-        <v>0.13282339643731489</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="11"/>
-        <v>13.28233964373149</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="12"/>
         <v>0.14595393097188597</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C10" s="5">
         <v>40</v>
       </c>
@@ -5049,50 +6427,50 @@
         <v>44</v>
       </c>
       <c r="E10" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="F10" s="5">
         <v>9.3000000000000007</v>
       </c>
       <c r="G10">
+        <f t="shared" si="4"/>
+        <v>390.6</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="5"/>
+        <v>16405.2</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="6"/>
+        <v>539.21967532499991</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>3.7954891891721947</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>0.87258504667371528</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>0.80855535302637249</v>
+      </c>
+      <c r="M10">
         <f t="shared" si="7"/>
-        <v>390.60000000000002</v>
-      </c>
-      <c r="H10">
+        <v>9.7538576071095506E-2</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="8"/>
-        <v>16405.200000000001</v>
-      </c>
-      <c r="I10">
+        <v>9.7538576071095502</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="9"/>
-        <v>539.21967532499991</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="3"/>
-        <v>3.7954891891721947</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="4"/>
-        <v>0.87258504667371528</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="5"/>
-        <v>0.80855535302637249</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="10"/>
-        <v>0.097538576071095506</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="11"/>
-        <v>9.7538576071095502</v>
-      </c>
-      <c r="O10">
-        <f t="shared" si="12"/>
-        <v>0.021118488276993426</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>2.1118488276993426E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C11" s="5">
         <v>45</v>
       </c>
@@ -5100,50 +6478,50 @@
         <v>49</v>
       </c>
       <c r="E11" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="F11" s="5">
         <v>6.79</v>
       </c>
       <c r="G11">
+        <f t="shared" si="4"/>
+        <v>319.13</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="5"/>
+        <v>14999.11</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="6"/>
+        <v>1080.4628935974999</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>3.9019726695746448</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>1.1551039021269824</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>0.87597605975949688</v>
+      </c>
+      <c r="M11">
         <f t="shared" si="7"/>
-        <v>319.13</v>
-      </c>
-      <c r="H11">
+        <v>6.7420706733124391E-2</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="8"/>
-        <v>14999.110000000001</v>
-      </c>
-      <c r="I11">
+        <v>6.7420706733124387</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="9"/>
-        <v>1080.4628935974999</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="3"/>
-        <v>3.9019726695746448</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="4"/>
-        <v>1.1551039021269824</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="5"/>
-        <v>0.87597605975949688</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="10"/>
-        <v>0.067420706733124391</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="11"/>
-        <v>6.7420706733124387</v>
-      </c>
-      <c r="O11">
-        <f t="shared" si="12"/>
-        <v>0.00034072920146272135</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>3.4072920146272135E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C12" s="5">
         <v>50</v>
       </c>
@@ -5151,50 +6529,50 @@
         <v>54</v>
       </c>
       <c r="E12" s="2">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="F12" s="5">
+        <v>5.82</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="4"/>
+        <v>302.64</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="5"/>
+        <v>15737.279999999999</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="6"/>
-        <v>52</v>
-      </c>
-      <c r="F12" s="5">
-        <v>5.8200000000000003</v>
-      </c>
-      <c r="G12">
+        <v>1805.7749516550002</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>3.9982007016691985</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>1.4104133021120717</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>0.92079116007419393</v>
+      </c>
+      <c r="M12">
         <f t="shared" si="7"/>
-        <v>302.63999999999999</v>
-      </c>
-      <c r="H12">
+        <v>4.4815100314697043E-2</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="8"/>
-        <v>15737.279999999999</v>
-      </c>
-      <c r="I12">
+        <v>4.4815100314697043</v>
+      </c>
+      <c r="O12">
         <f t="shared" si="9"/>
-        <v>1805.7749516550002</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="3"/>
-        <v>3.9982007016691985</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="4"/>
-        <v>1.4104133021120717</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="5"/>
-        <v>0.92079116007419393</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="10"/>
-        <v>0.044815100314697043</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="11"/>
-        <v>4.4815100314697043</v>
-      </c>
-      <c r="O12">
-        <f t="shared" si="12"/>
         <v>0.39976601263317824</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C13" s="5">
         <v>55</v>
       </c>
@@ -5202,50 +6580,50 @@
         <v>59</v>
       </c>
       <c r="E13" s="2">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+      <c r="F13" s="5">
+        <v>3.39</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="4"/>
+        <v>193.23000000000002</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="5"/>
+        <v>11014.11</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="6"/>
-        <v>57</v>
-      </c>
-      <c r="F13" s="5">
-        <v>3.3900000000000001</v>
-      </c>
-      <c r="G13">
+        <v>1733.6989187475001</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>4.0859763125515842</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>1.6432969853789869</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>0.94983924913020312</v>
+      </c>
+      <c r="M13">
         <f t="shared" si="7"/>
-        <v>193.23000000000002</v>
-      </c>
-      <c r="H13">
+        <v>2.9048089056009196E-2</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="8"/>
-        <v>11014.110000000001</v>
-      </c>
-      <c r="I13">
+        <v>2.9048089056009196</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="9"/>
-        <v>1733.6989187475001</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="3"/>
-        <v>4.0859763125515842</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="4"/>
-        <v>1.6432969853789869</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="5"/>
-        <v>0.94983924913020312</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="10"/>
-        <v>0.029048089056009196</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="11"/>
-        <v>2.9048089056009196</v>
-      </c>
-      <c r="O13">
-        <f t="shared" si="12"/>
-        <v>0.081041612627346979</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>8.1041612627346979E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C14" s="5">
         <v>60</v>
       </c>
@@ -5253,50 +6631,50 @@
         <v>64</v>
       </c>
       <c r="E14" s="2">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
+      <c r="F14" s="5">
+        <v>6.76</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="4"/>
+        <v>419.12</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="5"/>
+        <v>25985.439999999999</v>
+      </c>
+      <c r="I14">
         <f t="shared" si="6"/>
-        <v>62</v>
-      </c>
-      <c r="F14" s="5">
-        <v>6.7599999999999998</v>
-      </c>
-      <c r="G14">
+        <v>5154.9097252899992</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>4.1666652238017265</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>1.8573784444748331</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>0.96837133449191271</v>
+      </c>
+      <c r="M14">
         <f t="shared" si="7"/>
-        <v>419.12</v>
-      </c>
-      <c r="H14">
+        <v>1.8532085361709583E-2</v>
+      </c>
+      <c r="N14">
         <f t="shared" si="8"/>
-        <v>25985.439999999999</v>
-      </c>
-      <c r="I14">
+        <v>1.8532085361709583</v>
+      </c>
+      <c r="O14">
         <f t="shared" si="9"/>
-        <v>5154.9097252899992</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="3"/>
-        <v>4.1666652238017265</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="4"/>
-        <v>1.8573784444748331</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="5"/>
-        <v>0.96837133449191271</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="10"/>
-        <v>0.018532085361709583</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="11"/>
-        <v>1.8532085361709583</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="12"/>
         <v>12.991847382298308</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>37</v>
       </c>
@@ -5305,15 +6683,15 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <f t="shared" ref="G15:I15" si="13">SUM(G4:G14)</f>
+        <f t="shared" ref="G15:I15" si="10">SUM(G4:G14)</f>
         <v>3438.5499999999997</v>
       </c>
       <c r="H15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>136103.94999999998</v>
       </c>
       <c r="I15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>17867.688975000001</v>
       </c>
       <c r="N15" t="s">
@@ -5324,7 +6702,7 @@
         <v>16.126377174401828</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>39</v>
       </c>
@@ -5340,7 +6718,7 @@
         <v>15.507313055865453</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
         <v>41</v>
       </c>
@@ -5349,7 +6727,7 @@
         <v>34.3855</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E19" t="s">
         <v>42</v>
       </c>
@@ -5362,7 +6740,7 @@
         <v>180.48170681818183</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
         <v>43</v>
       </c>
@@ -5371,7 +6749,7 @@
         <v>1362.8443170681819</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E21" t="s">
         <v>44</v>
       </c>
@@ -5380,7 +6758,7 @@
         <v>3.4666053255876585</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
         <v>45</v>
       </c>
@@ -5389,7 +6767,7 @@
         <v>0.14205927660557893</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E23" t="s">
         <v>46</v>
       </c>
@@ -5399,33 +6777,32 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:L75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="18.28515625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="22"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="22.42578125"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="22"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="22.42578125"/>
-    <col customWidth="1" min="9" max="9" width="10.42578125"/>
-    <col customWidth="1" min="11" max="11" width="10.28515625"/>
-    <col customWidth="1" min="12" max="12" width="12.140625"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>47</v>
       </c>
@@ -5445,7 +6822,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>0</v>
       </c>
@@ -5461,15 +6838,15 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <f t="shared" ref="G5:G10" si="14">E5/$E$10*100</f>
+        <f t="shared" ref="G5:G10" si="0">E5/$E$10*100</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f t="shared" ref="H5:H10" si="15">F5/$F$10*100</f>
+        <f t="shared" ref="H5:H10" si="1">F5/$F$10*100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>100</v>
       </c>
@@ -5477,23 +6854,23 @@
         <v>80</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:E10" si="16">E5+C6</f>
+        <f t="shared" ref="E6:E10" si="2">E5+C6</f>
         <v>100</v>
       </c>
       <c r="F6">
-        <f t="shared" ref="F6:F10" si="17">F5+D6</f>
+        <f t="shared" ref="F6:F10" si="3">F5+D6</f>
         <v>80</v>
       </c>
       <c r="G6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="H6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>200</v>
       </c>
@@ -5501,23 +6878,23 @@
         <v>70</v>
       </c>
       <c r="E7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="F7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="G7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="H7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>400</v>
       </c>
@@ -5525,23 +6902,23 @@
         <v>50</v>
       </c>
       <c r="E8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>700</v>
       </c>
       <c r="F8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="G8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="H8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>500</v>
       </c>
@@ -5549,23 +6926,23 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="F9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>230</v>
       </c>
       <c r="G9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="H9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>800</v>
       </c>
@@ -5573,28 +6950,28 @@
         <v>20</v>
       </c>
       <c r="E10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
       <c r="F10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="G10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
-    <row r="30" ht="15.75">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" ht="39.75">
+    <row r="31" spans="1:12" ht="39" x14ac:dyDescent="0.25">
       <c r="C31" s="6" t="s">
         <v>53</v>
       </c>
@@ -5626,7 +7003,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="15.75">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -5644,7 +7021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="15.75">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="6" t="s">
         <v>63</v>
       </c>
@@ -5656,7 +7033,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="7">
-        <f t="shared" ref="F33:F37" si="18">E33/$E$37*100</f>
+        <f t="shared" ref="F33:F37" si="4">E33/$E$37*100</f>
         <v>4</v>
       </c>
       <c r="G33" s="7">
@@ -5678,7 +7055,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" ht="15.75">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="6" t="s">
         <v>64</v>
       </c>
@@ -5686,11 +7063,11 @@
         <v>150</v>
       </c>
       <c r="E34" s="7">
-        <f t="shared" ref="E34:E37" si="19">E33+D34</f>
+        <f t="shared" ref="E34:E37" si="5">E33+D34</f>
         <v>200</v>
       </c>
       <c r="F34" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="G34" s="7">
@@ -5712,7 +7089,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" ht="15.75">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="6" t="s">
         <v>65</v>
       </c>
@@ -5720,11 +7097,11 @@
         <v>250</v>
       </c>
       <c r="E35" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="5"/>
         <v>450</v>
       </c>
       <c r="F35" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="G35" s="7">
@@ -5746,7 +7123,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" ht="15.75">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="6" t="s">
         <v>66</v>
       </c>
@@ -5754,11 +7131,11 @@
         <v>350</v>
       </c>
       <c r="E36" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="5"/>
         <v>800</v>
       </c>
       <c r="F36" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="G36" s="7">
@@ -5780,7 +7157,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" ht="15.75">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C37" s="6" t="s">
         <v>67</v>
       </c>
@@ -5788,11 +7165,11 @@
         <v>450</v>
       </c>
       <c r="E37" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="F37" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="G37" s="7">
@@ -5814,17 +7191,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" ht="15.75">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>3</v>
       </c>
     </row>
-    <row r="59" ht="27">
+    <row r="59" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
       <c r="D59" s="6" t="s">
         <v>68</v>
       </c>
@@ -5835,7 +7212,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" ht="15.75">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D60" s="7">
         <v>0</v>
       </c>
@@ -5843,7 +7220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" ht="15.75">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D61" s="7">
         <v>10</v>
       </c>
@@ -5855,7 +7232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" ht="15.75">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D62" s="7">
         <v>20</v>
       </c>
@@ -5863,11 +7240,11 @@
         <v>5</v>
       </c>
       <c r="F62">
-        <f t="shared" ref="F62:F70" si="20">1/2*(E61+E62)*(D62-D61)</f>
+        <f t="shared" ref="F62:F70" si="6">1/2*(E61+E62)*(D62-D61)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="63" ht="15.75">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D63" s="7">
         <v>30</v>
       </c>
@@ -5875,11 +7252,11 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>75</v>
       </c>
     </row>
-    <row r="64" ht="15.75">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D64" s="7">
         <v>40</v>
       </c>
@@ -5887,11 +7264,11 @@
         <v>15</v>
       </c>
       <c r="F64">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
     </row>
-    <row r="65" ht="15.75">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="7">
         <v>50</v>
       </c>
@@ -5899,11 +7276,11 @@
         <v>25</v>
       </c>
       <c r="F65">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
     </row>
-    <row r="66" ht="15.75">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="7">
         <v>60</v>
       </c>
@@ -5911,11 +7288,11 @@
         <v>35</v>
       </c>
       <c r="F66">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
     </row>
-    <row r="67" ht="15.75">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D67" s="7">
         <v>70</v>
       </c>
@@ -5923,11 +7300,11 @@
         <v>45</v>
       </c>
       <c r="F67">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>400</v>
       </c>
     </row>
-    <row r="68" ht="15.75">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="7">
         <v>80</v>
       </c>
@@ -5935,11 +7312,11 @@
         <v>55</v>
       </c>
       <c r="F68">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
     </row>
-    <row r="69" ht="15.75">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="7">
         <v>90</v>
       </c>
@@ -5947,11 +7324,11 @@
         <v>75</v>
       </c>
       <c r="F69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
     </row>
-    <row r="70" ht="15.75">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="7">
         <v>100</v>
       </c>
@@ -5959,11 +7336,11 @@
         <v>100</v>
       </c>
       <c r="F70">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>875</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H73" t="s">
         <v>70</v>
       </c>
@@ -5972,7 +7349,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H74" t="s">
         <v>71</v>
       </c>
@@ -5981,7 +7358,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H75" t="s">
         <v>72</v>
       </c>
@@ -5991,22 +7368,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C4:K20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="12"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>73</v>
       </c>
@@ -6023,18 +7399,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>136</v>
       </c>
       <c r="D5">
-        <v>54300.099999999999</v>
+        <v>54300.1</v>
       </c>
       <c r="E5">
         <v>29100.799999999999</v>
       </c>
       <c r="F5">
-        <f t="shared" ref="F5:G8" si="21">LN(D5)</f>
+        <f t="shared" ref="F5:G8" si="0">LN(D5)</f>
         <v>10.902281347540956</v>
       </c>
       <c r="G5">
@@ -6042,45 +7418,45 @@
         <v>10.278520944190637</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>179</v>
       </c>
       <c r="D6">
-        <v>68100.300000000003</v>
+        <v>68100.3</v>
       </c>
       <c r="E6">
-        <v>33100.599999999999</v>
+        <v>33100.6</v>
       </c>
       <c r="F6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="0"/>
         <v>11.128736897414244</v>
       </c>
       <c r="G6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="0"/>
         <v>10.407306688089081</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>111</v>
       </c>
       <c r="D7">
-        <v>86100.899999999994</v>
+        <v>86100.9</v>
       </c>
       <c r="E7">
         <v>37400.400000000001</v>
       </c>
       <c r="F7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="0"/>
         <v>11.363275143322863</v>
       </c>
       <c r="G7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="0"/>
         <v>10.529436678532596</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>22</v>
       </c>
@@ -6088,23 +7464,23 @@
         <v>123200</v>
       </c>
       <c r="E8">
-        <v>40700.099999999999</v>
+        <v>40700.1</v>
       </c>
       <c r="F8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="0"/>
         <v>11.721564330081556</v>
       </c>
       <c r="G8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="0"/>
         <v>10.613985828430124</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>73</v>
       </c>
@@ -6127,7 +7503,7 @@
         <v>0.47584445659515778</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>81</v>
       </c>
@@ -6150,7 +7526,7 @@
         <v>5.1042800678092295</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>84</v>
       </c>
@@ -6170,10 +7546,10 @@
       </c>
       <c r="K16">
         <f>D14/(D14*G16-G14^2)</f>
-        <v>0.048404831444691911</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>4.8404831444691911E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
         <v>87</v>
       </c>
@@ -6189,7 +7565,7 @@
         <v>0.220010980282103</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="6:11" x14ac:dyDescent="0.25">
       <c r="J20" t="s">
         <v>89</v>
       </c>
@@ -6199,11 +7575,3137 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:M115"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="8">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="8">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="8">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="8">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="8">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="8">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="8">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="8">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="8">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="8">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="8">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="8">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="8">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="8">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="8">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="8">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="14"/>
+    </row>
+    <row r="29" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="31" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D31" s="10"/>
+    </row>
+    <row r="32" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="8">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="8">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D33" s="10">
+        <f>AVERAGE(C29:C36)</f>
+        <v>18.137499999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D34" s="10"/>
+    </row>
+    <row r="35" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="D35" s="10"/>
+    </row>
+    <row r="36" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="8">
+        <v>17.3</v>
+      </c>
+      <c r="D36" s="10"/>
+    </row>
+    <row r="37" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="9">
+        <v>21.4</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D38" s="10"/>
+    </row>
+    <row r="39" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="D40" s="10"/>
+    </row>
+    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C41" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="D41" s="10">
+        <f>AVERAGE(C38:C45)</f>
+        <v>20.325000000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B42" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="8">
+        <v>22.2</v>
+      </c>
+      <c r="D42" s="10"/>
+    </row>
+    <row r="43" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="8">
+        <v>21.5</v>
+      </c>
+      <c r="D44" s="10"/>
+    </row>
+    <row r="45" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="D45" s="10"/>
+    </row>
+    <row r="50" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B51" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="20"/>
+    </row>
+    <row r="52" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="21"/>
+    </row>
+    <row r="53" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B53" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D53" s="10">
+        <f>(C53+C52)/2</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E53" s="10">
+        <f>(D53+D54)/2</f>
+        <v>19.725000000000001</v>
+      </c>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="20"/>
+    </row>
+    <row r="54" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B54" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D54" s="10">
+        <f t="shared" ref="D54:D68" si="0">(C54+C53)/2</f>
+        <v>19.350000000000001</v>
+      </c>
+      <c r="E54" s="10">
+        <f t="shared" ref="E54:E66" si="1">(D54+D55)/2</f>
+        <v>18.150000000000002</v>
+      </c>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+    </row>
+    <row r="55" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B55" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="8">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D55" s="10">
+        <f t="shared" si="0"/>
+        <v>16.950000000000003</v>
+      </c>
+      <c r="E55" s="10">
+        <f t="shared" si="1"/>
+        <v>16.900000000000002</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="J55" s="19"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="20"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B56" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="8">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D56" s="10">
+        <f t="shared" si="0"/>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="E56" s="10">
+        <f t="shared" si="1"/>
+        <v>17.275000000000002</v>
+      </c>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="20"/>
+    </row>
+    <row r="57" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D57" s="10">
+        <f t="shared" si="0"/>
+        <v>17.700000000000003</v>
+      </c>
+      <c r="E57" s="10">
+        <f t="shared" si="1"/>
+        <v>17.875</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B58" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="D58" s="10">
+        <f t="shared" si="0"/>
+        <v>18.05</v>
+      </c>
+      <c r="E58" s="10">
+        <f t="shared" si="1"/>
+        <v>17.925000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="8">
+        <v>17.3</v>
+      </c>
+      <c r="D59" s="10">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="E59" s="10">
+        <f t="shared" si="1"/>
+        <v>18.575000000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B60" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C60" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="D60" s="10">
+        <f t="shared" si="0"/>
+        <v>19.350000000000001</v>
+      </c>
+      <c r="E60" s="10">
+        <f t="shared" si="1"/>
+        <v>19.850000000000001</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D61" s="10">
+        <f t="shared" si="0"/>
+        <v>20.350000000000001</v>
+      </c>
+      <c r="E61" s="10">
+        <f t="shared" si="1"/>
+        <v>19.525000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D62" s="10">
+        <f t="shared" si="0"/>
+        <v>18.700000000000003</v>
+      </c>
+      <c r="E62" s="10">
+        <f t="shared" si="1"/>
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C63" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="D63" s="10">
+        <f t="shared" si="0"/>
+        <v>18.8</v>
+      </c>
+      <c r="E63" s="10">
+        <f t="shared" si="1"/>
+        <v>19.075000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="D64" s="10">
+        <f t="shared" si="0"/>
+        <v>19.350000000000001</v>
+      </c>
+      <c r="E64" s="10">
+        <f t="shared" si="1"/>
+        <v>20.024999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C65" s="8">
+        <v>22.2</v>
+      </c>
+      <c r="D65" s="10">
+        <f t="shared" si="0"/>
+        <v>20.7</v>
+      </c>
+      <c r="E65" s="10">
+        <f t="shared" si="1"/>
+        <v>21.125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B66" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D66" s="10">
+        <f t="shared" si="0"/>
+        <v>21.549999999999997</v>
+      </c>
+      <c r="E66" s="10">
+        <f t="shared" si="1"/>
+        <v>21.375</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B67" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C67" s="8">
+        <v>21.5</v>
+      </c>
+      <c r="D67" s="10">
+        <f t="shared" si="0"/>
+        <v>21.2</v>
+      </c>
+      <c r="E67" s="10">
+        <f>(D67+D68)/2</f>
+        <v>21.45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B68" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="D68" s="10">
+        <f t="shared" si="0"/>
+        <v>21.7</v>
+      </c>
+      <c r="E68" s="10"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" s="8">
+        <v>0</v>
+      </c>
+      <c r="C75" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D75">
+        <f t="array" ref="D75:D91">TREND(C75:C91, B75:B91)</f>
+        <v>17.649019607843137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" s="8">
+        <v>1</v>
+      </c>
+      <c r="C76" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D76">
+        <v>17.862745098039216</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" s="8">
+        <v>2</v>
+      </c>
+      <c r="C77" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D77">
+        <v>18.076470588235292</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78" s="8">
+        <v>3</v>
+      </c>
+      <c r="C78" s="8">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D78">
+        <v>18.290196078431372</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" s="8">
+        <v>4</v>
+      </c>
+      <c r="C79" s="8">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D79">
+        <v>18.503921568627451</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80" s="8">
+        <v>5</v>
+      </c>
+      <c r="C80" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D80">
+        <v>18.717647058823527</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" s="8">
+        <v>6</v>
+      </c>
+      <c r="C81" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="D81">
+        <v>18.931372549019606</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" s="8">
+        <v>7</v>
+      </c>
+      <c r="C82" s="8">
+        <v>17.3</v>
+      </c>
+      <c r="D82">
+        <v>19.145098039215686</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="8">
+        <v>8</v>
+      </c>
+      <c r="C83" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="D83">
+        <v>19.358823529411762</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" s="8">
+        <v>9</v>
+      </c>
+      <c r="C84" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D84">
+        <v>19.572549019607841</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85" s="8">
+        <v>10</v>
+      </c>
+      <c r="C85" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D85">
+        <v>19.786274509803921</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="8">
+        <v>11</v>
+      </c>
+      <c r="C86" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="D86">
+        <v>19.999999999999996</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B87" s="8">
+        <v>12</v>
+      </c>
+      <c r="C87" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="D87">
+        <v>20.213725490196076</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88" s="8">
+        <v>13</v>
+      </c>
+      <c r="C88" s="8">
+        <v>22.2</v>
+      </c>
+      <c r="D88">
+        <v>20.427450980392155</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B89" s="8">
+        <v>14</v>
+      </c>
+      <c r="C89" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D89">
+        <v>20.641176470588231</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B90" s="8">
+        <v>15</v>
+      </c>
+      <c r="C90" s="8">
+        <v>21.5</v>
+      </c>
+      <c r="D90">
+        <v>20.854901960784311</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91" s="8">
+        <v>16</v>
+      </c>
+      <c r="C91" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="D91">
+        <v>21.06862745098039</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B97" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D97" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="I97" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="J97">
+        <f>E114</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B98" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C98" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D98" s="10">
+        <f>IF(C98&lt;$C$115, 0, 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="10">
+        <v>0</v>
+      </c>
+      <c r="I98" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="J98">
+        <f>17-J99</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C99" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D99" s="10">
+        <f t="shared" ref="D99:D114" si="2">IF(C99&lt;$C$115, 0, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="E99" s="10">
+        <f>IF(D99=D98, E98, E98+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I99" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="J99">
+        <f>SUM(D98:D114)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B100" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C100" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D100" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E100" s="10">
+        <f t="shared" ref="E100:E114" si="3">IF(D100=D99, E99, E99+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I100" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="J100">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B101" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C101" s="8">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D101" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E101" s="10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B102" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C102" s="8">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D102" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E102" s="10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B103" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C103" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="D103" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E103" s="10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B104" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C104" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="D104" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E104" s="10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B105" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C105" s="8">
+        <v>17.3</v>
+      </c>
+      <c r="D105" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E105" s="10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I105" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="J105">
+        <v>-1.1583158907100046</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B106" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="D106" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E106" s="10">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I106" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="J106">
+        <f>_xlfn.NORM.S.DIST(J105, TRUE)</f>
+        <v>0.1233675744503831</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B107" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D107" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E107" s="10">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B108" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C108" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D108" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E108" s="10">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B109" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C109" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="D109" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E109" s="10">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B110" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C110" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="D110" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E110" s="10">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B111" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C111" s="8">
+        <v>22.2</v>
+      </c>
+      <c r="D111" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E111" s="10">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B112" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C112" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="D112" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E112" s="10">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B113" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" s="8">
+        <v>21.5</v>
+      </c>
+      <c r="D113" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E113" s="10">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B114" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C114" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="D114" s="10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E114" s="10">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B115" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C115" s="10">
+        <f>AVERAGE(C98:C114)</f>
+        <v>19.358823529411762</v>
+      </c>
+      <c r="D115" s="10"/>
+      <c r="E115" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:AB58"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="M3" t="s">
+        <v>134</v>
+      </c>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="20"/>
+    </row>
+    <row r="4" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="24">
+        <v>1</v>
+      </c>
+      <c r="C4" s="24">
+        <v>6</v>
+      </c>
+      <c r="D4" s="24">
+        <v>110</v>
+      </c>
+      <c r="E4" s="24">
+        <v>30</v>
+      </c>
+      <c r="F4" s="10">
+        <f>LN(C4)</f>
+        <v>1.791759469228055</v>
+      </c>
+      <c r="G4" s="10">
+        <f>LN(D4)</f>
+        <v>4.7004803657924166</v>
+      </c>
+      <c r="H4" s="10">
+        <f>LN(E4)</f>
+        <v>3.4011973816621555</v>
+      </c>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B5" s="24">
+        <v>2</v>
+      </c>
+      <c r="C5" s="24">
+        <v>12</v>
+      </c>
+      <c r="D5" s="24">
+        <v>120</v>
+      </c>
+      <c r="E5" s="24">
+        <v>40</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" ref="F5:F18" si="0">LN(C5)</f>
+        <v>2.4849066497880004</v>
+      </c>
+      <c r="G5" s="10">
+        <f t="shared" ref="G5:G18" si="1">LN(D5)</f>
+        <v>4.7874917427820458</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" ref="H5:H18" si="2">LN(E5)</f>
+        <v>3.6888794541139363</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="N5" s="29"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="24">
+        <v>3</v>
+      </c>
+      <c r="C6" s="24">
+        <v>19</v>
+      </c>
+      <c r="D6" s="24">
+        <v>143</v>
+      </c>
+      <c r="E6" s="24">
+        <v>42</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="0"/>
+        <v>2.9444389791664403</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" si="1"/>
+        <v>4.962844630259907</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" si="2"/>
+        <v>3.7376696182833684</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="N6" s="26">
+        <v>0.95636074660553672</v>
+      </c>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B7" s="24">
+        <v>4</v>
+      </c>
+      <c r="C7" s="24">
+        <v>25</v>
+      </c>
+      <c r="D7" s="24">
+        <v>150</v>
+      </c>
+      <c r="E7" s="24">
+        <v>40</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="0"/>
+        <v>3.2188758248682006</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0106352940962555</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" si="2"/>
+        <v>3.6888794541139363</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="N7" s="26">
+        <v>0.91462587764789971</v>
+      </c>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B8" s="24">
+        <v>5</v>
+      </c>
+      <c r="C8" s="24">
+        <v>30</v>
+      </c>
+      <c r="D8" s="24">
+        <v>152</v>
+      </c>
+      <c r="E8" s="24">
+        <v>51</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4011973816621555</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0238805208462765</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="2"/>
+        <v>3.9318256327243257</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" s="26">
+        <v>0.90039685725588292</v>
+      </c>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B9" s="24">
+        <v>6</v>
+      </c>
+      <c r="C9" s="24">
+        <v>36</v>
+      </c>
+      <c r="D9" s="24">
+        <v>162</v>
+      </c>
+      <c r="E9" s="24">
+        <v>59</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="0"/>
+        <v>3.5835189384561099</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0875963352323836</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" si="2"/>
+        <v>4.0775374439057197</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" s="26">
+        <v>0.19388888356372988</v>
+      </c>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+    </row>
+    <row r="10" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="24">
+        <v>7</v>
+      </c>
+      <c r="C10" s="24">
+        <v>38</v>
+      </c>
+      <c r="D10" s="24">
+        <v>180</v>
+      </c>
+      <c r="E10" s="24">
+        <v>60</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="0"/>
+        <v>3.6375861597263857</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="1"/>
+        <v>5.1929568508902104</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="2"/>
+        <v>4.0943445622221004</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" s="27">
+        <v>15</v>
+      </c>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B11" s="24">
+        <v>8</v>
+      </c>
+      <c r="C11" s="24">
+        <v>43</v>
+      </c>
+      <c r="D11" s="24">
+        <v>182</v>
+      </c>
+      <c r="E11" s="24">
+        <v>63</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="0"/>
+        <v>3.7612001156935624</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="1"/>
+        <v>5.2040066870767951</v>
+      </c>
+      <c r="H11" s="10">
+        <f>LN(E11)</f>
+        <v>4.1431347263915326</v>
+      </c>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+    </row>
+    <row r="12" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="24">
+        <v>9</v>
+      </c>
+      <c r="C12" s="24">
+        <v>44</v>
+      </c>
+      <c r="D12" s="24">
+        <v>180</v>
+      </c>
+      <c r="E12" s="24">
+        <v>61</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="0"/>
+        <v>3.784189633918261</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="1"/>
+        <v>5.1929568508902104</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="2"/>
+        <v>4.1108738641733114</v>
+      </c>
+      <c r="M12" t="s">
+        <v>141</v>
+      </c>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B13" s="24">
+        <v>10</v>
+      </c>
+      <c r="C13" s="24">
+        <v>49</v>
+      </c>
+      <c r="D13" s="24">
+        <v>175</v>
+      </c>
+      <c r="E13" s="24">
+        <v>63</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" si="0"/>
+        <v>3.8918202981106265</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="1"/>
+        <v>5.1647859739235145</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" si="2"/>
+        <v>4.1431347263915326</v>
+      </c>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="O13" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="P13" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="R13" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B14" s="24">
+        <v>11</v>
+      </c>
+      <c r="C14" s="24">
+        <v>50</v>
+      </c>
+      <c r="D14" s="24">
+        <v>195</v>
+      </c>
+      <c r="E14" s="24">
+        <v>85</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="0"/>
+        <v>3.912023005428146</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="1"/>
+        <v>5.2729995585637468</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" si="2"/>
+        <v>4.4426512564903167</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="N14" s="26">
+        <v>2</v>
+      </c>
+      <c r="O14" s="26">
+        <v>4.8328609347704568</v>
+      </c>
+      <c r="P14" s="26">
+        <v>2.4164304673852284</v>
+      </c>
+      <c r="Q14" s="26">
+        <v>64.278906941552833</v>
+      </c>
+      <c r="R14" s="26">
+        <v>3.8721976132550833E-7</v>
+      </c>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B15" s="24">
+        <v>12</v>
+      </c>
+      <c r="C15" s="24">
+        <v>52</v>
+      </c>
+      <c r="D15" s="24">
+        <v>196</v>
+      </c>
+      <c r="E15" s="24">
+        <v>90</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="0"/>
+        <v>3.9512437185814275</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="1"/>
+        <v>5.2781146592305168</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" si="2"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="N15" s="26">
+        <v>12</v>
+      </c>
+      <c r="O15" s="26">
+        <v>0.45111479003507515</v>
+      </c>
+      <c r="P15" s="26">
+        <v>3.7592899169589598E-2</v>
+      </c>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+    </row>
+    <row r="16" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="24">
+        <v>13</v>
+      </c>
+      <c r="C16" s="24">
+        <v>54</v>
+      </c>
+      <c r="D16" s="24">
+        <v>183</v>
+      </c>
+      <c r="E16" s="24">
+        <v>98</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="0"/>
+        <v>3.9889840465642745</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="1"/>
+        <v>5.2094861528414214</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="2"/>
+        <v>4.5849674786705723</v>
+      </c>
+      <c r="M16" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="27">
+        <v>14</v>
+      </c>
+      <c r="O16" s="27">
+        <v>5.2839757248055319</v>
+      </c>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+    </row>
+    <row r="17" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="24">
+        <v>14</v>
+      </c>
+      <c r="C17" s="24">
+        <v>41</v>
+      </c>
+      <c r="D17" s="24">
+        <v>190</v>
+      </c>
+      <c r="E17" s="24">
+        <v>90</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="0"/>
+        <v>3.713572066704308</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="1"/>
+        <v>5.2470240721604862</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" si="2"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B18" s="24">
+        <v>15</v>
+      </c>
+      <c r="C18" s="24">
+        <v>35</v>
+      </c>
+      <c r="D18" s="24">
+        <v>150</v>
+      </c>
+      <c r="E18" s="24">
+        <v>80</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" si="0"/>
+        <v>3.5553480614894135</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0106352940962555</v>
+      </c>
+      <c r="H18" s="10">
+        <f t="shared" si="2"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="P18" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q18" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="R18" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="S18" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="T18" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="U18" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="V18" s="30"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M19" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="N19" s="26">
+        <v>-11.912101672451231</v>
+      </c>
+      <c r="O19" s="26">
+        <v>2.004357268743898</v>
+      </c>
+      <c r="P19" s="26">
+        <v>-5.9431029877804038</v>
+      </c>
+      <c r="Q19" s="26">
+        <v>6.7854166077835272E-5</v>
+      </c>
+      <c r="R19" s="26">
+        <v>-16.2792210048272</v>
+      </c>
+      <c r="S19" s="26">
+        <v>-7.5449823400752605</v>
+      </c>
+      <c r="T19" s="26">
+        <v>-16.2792210048272</v>
+      </c>
+      <c r="U19" s="26">
+        <v>-7.5449823400752605</v>
+      </c>
+      <c r="V19" s="26"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M20" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="N20" s="26">
+        <v>2.7219009763464044</v>
+      </c>
+      <c r="O20" s="26">
+        <v>0.56710720391451808</v>
+      </c>
+      <c r="P20" s="26">
+        <v>4.7996233473286747</v>
+      </c>
+      <c r="Q20" s="26">
+        <v>4.3381461102204652E-4</v>
+      </c>
+      <c r="R20" s="26">
+        <v>1.4862805246607433</v>
+      </c>
+      <c r="S20" s="26">
+        <v>3.9575214280320656</v>
+      </c>
+      <c r="T20" s="26">
+        <v>1.4862805246607433</v>
+      </c>
+      <c r="U20" s="26">
+        <v>3.9575214280320656</v>
+      </c>
+      <c r="V20" s="26"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+    </row>
+    <row r="21" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="N21" s="27">
+        <v>0.36622849836733257</v>
+      </c>
+      <c r="O21" s="27">
+        <v>0.27979501337555757</v>
+      </c>
+      <c r="P21" s="27">
+        <v>1.3089171745736541</v>
+      </c>
+      <c r="Q21" s="27">
+        <v>0.21507415031318358</v>
+      </c>
+      <c r="R21" s="27">
+        <v>-0.24339246645224605</v>
+      </c>
+      <c r="S21" s="27">
+        <v>0.97584946318691124</v>
+      </c>
+      <c r="T21" s="27">
+        <v>-0.24339246645224605</v>
+      </c>
+      <c r="U21" s="27">
+        <v>0.97584946318691124</v>
+      </c>
+      <c r="V21" s="26"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L24" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="M24" s="10">
+        <f>EXP(N19)</f>
+        <v>6.7087247818839355E-6</v>
+      </c>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L25" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="M25" s="10">
+        <f>N20</f>
+        <v>2.7219009763464044</v>
+      </c>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L26" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="M26" s="33">
+        <f>N21</f>
+        <v>0.36622849836733257</v>
+      </c>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M27" s="31"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M28" s="32"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B34" s="16"/>
+      <c r="C34" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="H34" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="M34" t="s">
+        <v>134</v>
+      </c>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="20"/>
+      <c r="AB34" s="20"/>
+    </row>
+    <row r="35" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="24">
+        <v>1</v>
+      </c>
+      <c r="C35" s="24">
+        <v>6</v>
+      </c>
+      <c r="D35" s="24">
+        <v>110</v>
+      </c>
+      <c r="E35" s="24">
+        <v>30</v>
+      </c>
+      <c r="F35" s="10">
+        <f>LN(C35)</f>
+        <v>1.791759469228055</v>
+      </c>
+      <c r="G35" s="10">
+        <f>LN(D35)</f>
+        <v>4.7004803657924166</v>
+      </c>
+      <c r="H35" s="10">
+        <f>LN(E35)</f>
+        <v>3.4011973816621555</v>
+      </c>
+      <c r="I35" s="10">
+        <f>(G35-H35)^2</f>
+        <v>1.6881362728504363</v>
+      </c>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B36" s="24">
+        <v>2</v>
+      </c>
+      <c r="C36" s="24">
+        <v>12</v>
+      </c>
+      <c r="D36" s="24">
+        <v>120</v>
+      </c>
+      <c r="E36" s="24">
+        <v>40</v>
+      </c>
+      <c r="F36" s="10">
+        <f t="shared" ref="F36:F49" si="3">LN(C36)</f>
+        <v>2.4849066497880004</v>
+      </c>
+      <c r="G36" s="10">
+        <f t="shared" ref="G36:G49" si="4">LN(D36)</f>
+        <v>4.7874917427820458</v>
+      </c>
+      <c r="H36" s="10">
+        <f t="shared" ref="H36:H49" si="5">LN(E36)</f>
+        <v>3.6888794541139363</v>
+      </c>
+      <c r="I36" s="10">
+        <f t="shared" ref="I36:I49" si="6">(G36-H36)^2</f>
+        <v>1.2069489608125816</v>
+      </c>
+      <c r="M36" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="N36" s="29"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B37" s="24">
+        <v>3</v>
+      </c>
+      <c r="C37" s="24">
+        <v>19</v>
+      </c>
+      <c r="D37" s="24">
+        <v>143</v>
+      </c>
+      <c r="E37" s="24">
+        <v>42</v>
+      </c>
+      <c r="F37" s="10">
+        <f t="shared" si="3"/>
+        <v>2.9444389791664403</v>
+      </c>
+      <c r="G37" s="10">
+        <f t="shared" si="4"/>
+        <v>4.962844630259907</v>
+      </c>
+      <c r="H37" s="10">
+        <f t="shared" si="5"/>
+        <v>3.7376696182833684</v>
+      </c>
+      <c r="I37" s="10">
+        <f t="shared" si="6"/>
+        <v>1.5010538099717115</v>
+      </c>
+      <c r="M37" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="N37" s="26">
+        <v>0.95674507977866774</v>
+      </c>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+      <c r="Z37" s="20"/>
+      <c r="AA37" s="20"/>
+      <c r="AB37" s="20"/>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B38" s="24">
+        <v>4</v>
+      </c>
+      <c r="C38" s="24">
+        <v>25</v>
+      </c>
+      <c r="D38" s="24">
+        <v>150</v>
+      </c>
+      <c r="E38" s="24">
+        <v>40</v>
+      </c>
+      <c r="F38" s="10">
+        <f t="shared" si="3"/>
+        <v>3.2188758248682006</v>
+      </c>
+      <c r="G38" s="10">
+        <f t="shared" si="4"/>
+        <v>5.0106352940962555</v>
+      </c>
+      <c r="H38" s="10">
+        <f t="shared" si="5"/>
+        <v>3.6888794541139363</v>
+      </c>
+      <c r="I38" s="10">
+        <f t="shared" si="6"/>
+        <v>1.7470385005273663</v>
+      </c>
+      <c r="M38" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="N38" s="26">
+        <v>0.91536114768068921</v>
+      </c>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B39" s="24">
+        <v>5</v>
+      </c>
+      <c r="C39" s="24">
+        <v>30</v>
+      </c>
+      <c r="D39" s="24">
+        <v>152</v>
+      </c>
+      <c r="E39" s="24">
+        <v>51</v>
+      </c>
+      <c r="F39" s="10">
+        <f t="shared" si="3"/>
+        <v>3.4011973816621555</v>
+      </c>
+      <c r="G39" s="10">
+        <f t="shared" si="4"/>
+        <v>5.0238805208462765</v>
+      </c>
+      <c r="H39" s="10">
+        <f t="shared" si="5"/>
+        <v>3.9318256327243257</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="6"/>
+        <v>1.1925838786710463</v>
+      </c>
+      <c r="M39" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="N39" s="26">
+        <v>0.89227782432087721</v>
+      </c>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B40" s="24">
+        <v>6</v>
+      </c>
+      <c r="C40" s="24">
+        <v>36</v>
+      </c>
+      <c r="D40" s="24">
+        <v>162</v>
+      </c>
+      <c r="E40" s="24">
+        <v>59</v>
+      </c>
+      <c r="F40" s="10">
+        <f t="shared" si="3"/>
+        <v>3.5835189384561099</v>
+      </c>
+      <c r="G40" s="10">
+        <f t="shared" si="4"/>
+        <v>5.0875963352323836</v>
+      </c>
+      <c r="H40" s="10">
+        <f t="shared" si="5"/>
+        <v>4.0775374439057197</v>
+      </c>
+      <c r="I40" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0202189639480495</v>
+      </c>
+      <c r="M40" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="N40" s="26">
+        <v>0.20163640567539978</v>
+      </c>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="20"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+    </row>
+    <row r="41" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="24">
+        <v>7</v>
+      </c>
+      <c r="C41" s="24">
+        <v>38</v>
+      </c>
+      <c r="D41" s="24">
+        <v>180</v>
+      </c>
+      <c r="E41" s="24">
+        <v>60</v>
+      </c>
+      <c r="F41" s="10">
+        <f t="shared" si="3"/>
+        <v>3.6375861597263857</v>
+      </c>
+      <c r="G41" s="10">
+        <f t="shared" si="4"/>
+        <v>5.1929568508902104</v>
+      </c>
+      <c r="H41" s="10">
+        <f t="shared" si="5"/>
+        <v>4.0943445622221004</v>
+      </c>
+      <c r="I41" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2069489608125827</v>
+      </c>
+      <c r="M41" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="N41" s="27">
+        <v>15</v>
+      </c>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B42" s="24">
+        <v>8</v>
+      </c>
+      <c r="C42" s="24">
+        <v>43</v>
+      </c>
+      <c r="D42" s="24">
+        <v>182</v>
+      </c>
+      <c r="E42" s="24">
+        <v>63</v>
+      </c>
+      <c r="F42" s="10">
+        <f t="shared" si="3"/>
+        <v>3.7612001156935624</v>
+      </c>
+      <c r="G42" s="10">
+        <f t="shared" si="4"/>
+        <v>5.2040066870767951</v>
+      </c>
+      <c r="H42" s="10">
+        <f>LN(E42)</f>
+        <v>4.1431347263915326</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="6"/>
+        <v>1.1254493169681934</v>
+      </c>
+      <c r="V42" s="20"/>
+      <c r="W42" s="20"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="20"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
+    </row>
+    <row r="43" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="24">
+        <v>9</v>
+      </c>
+      <c r="C43" s="24">
+        <v>44</v>
+      </c>
+      <c r="D43" s="24">
+        <v>180</v>
+      </c>
+      <c r="E43" s="24">
+        <v>61</v>
+      </c>
+      <c r="F43" s="10">
+        <f t="shared" si="3"/>
+        <v>3.784189633918261</v>
+      </c>
+      <c r="G43" s="10">
+        <f t="shared" si="4"/>
+        <v>5.1929568508902104</v>
+      </c>
+      <c r="H43" s="10">
+        <f t="shared" ref="H43:H49" si="7">LN(E43)</f>
+        <v>4.1108738641733114</v>
+      </c>
+      <c r="I43" s="10">
+        <f t="shared" si="6"/>
+        <v>1.1709035901421647</v>
+      </c>
+      <c r="M43" t="s">
+        <v>141</v>
+      </c>
+      <c r="V43" s="20"/>
+      <c r="W43" s="20"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
+      <c r="Z43" s="20"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B44" s="24">
+        <v>10</v>
+      </c>
+      <c r="C44" s="24">
+        <v>49</v>
+      </c>
+      <c r="D44" s="24">
+        <v>175</v>
+      </c>
+      <c r="E44" s="24">
+        <v>63</v>
+      </c>
+      <c r="F44" s="10">
+        <f t="shared" si="3"/>
+        <v>3.8918202981106265</v>
+      </c>
+      <c r="G44" s="10">
+        <f t="shared" si="4"/>
+        <v>5.1647859739235145</v>
+      </c>
+      <c r="H44" s="10">
+        <f t="shared" si="7"/>
+        <v>4.1431347263915326</v>
+      </c>
+      <c r="I44" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0437712715836549</v>
+      </c>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="O44" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="P44" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q44" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="R44" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="20"/>
+      <c r="AA44" s="20"/>
+      <c r="AB44" s="20"/>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B45" s="24">
+        <v>11</v>
+      </c>
+      <c r="C45" s="24">
+        <v>50</v>
+      </c>
+      <c r="D45" s="24">
+        <v>195</v>
+      </c>
+      <c r="E45" s="24">
+        <v>85</v>
+      </c>
+      <c r="F45" s="10">
+        <f t="shared" si="3"/>
+        <v>3.912023005428146</v>
+      </c>
+      <c r="G45" s="10">
+        <f t="shared" si="4"/>
+        <v>5.2729995585637468</v>
+      </c>
+      <c r="H45" s="10">
+        <f t="shared" si="7"/>
+        <v>4.4426512564903167</v>
+      </c>
+      <c r="I45" s="10">
+        <f t="shared" si="6"/>
+        <v>0.68947830275622835</v>
+      </c>
+      <c r="M45" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="N45" s="26">
+        <v>3</v>
+      </c>
+      <c r="O45" s="26">
+        <v>4.8367460837748935</v>
+      </c>
+      <c r="P45" s="26">
+        <v>1.6122486945916312</v>
+      </c>
+      <c r="Q45" s="26">
+        <v>39.654651689987134</v>
+      </c>
+      <c r="R45" s="26">
+        <v>3.4360344662519289E-6</v>
+      </c>
+      <c r="V45" s="20"/>
+      <c r="W45" s="20"/>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
+      <c r="Z45" s="20"/>
+      <c r="AA45" s="20"/>
+      <c r="AB45" s="20"/>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B46" s="24">
+        <v>12</v>
+      </c>
+      <c r="C46" s="24">
+        <v>52</v>
+      </c>
+      <c r="D46" s="24">
+        <v>196</v>
+      </c>
+      <c r="E46" s="24">
+        <v>90</v>
+      </c>
+      <c r="F46" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9512437185814275</v>
+      </c>
+      <c r="G46" s="10">
+        <f t="shared" si="4"/>
+        <v>5.2781146592305168</v>
+      </c>
+      <c r="H46" s="10">
+        <f t="shared" si="7"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="I46" s="10">
+        <f t="shared" si="6"/>
+        <v>0.60575865574702104</v>
+      </c>
+      <c r="M46" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="N46" s="26">
+        <v>11</v>
+      </c>
+      <c r="O46" s="26">
+        <v>0.44722964103063834</v>
+      </c>
+      <c r="P46" s="26">
+        <v>4.0657240093694397E-2</v>
+      </c>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="26"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="20"/>
+      <c r="AA46" s="20"/>
+      <c r="AB46" s="20"/>
+    </row>
+    <row r="47" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="24">
+        <v>13</v>
+      </c>
+      <c r="C47" s="24">
+        <v>54</v>
+      </c>
+      <c r="D47" s="24">
+        <v>183</v>
+      </c>
+      <c r="E47" s="24">
+        <v>98</v>
+      </c>
+      <c r="F47" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9889840465642745</v>
+      </c>
+      <c r="G47" s="10">
+        <f t="shared" si="4"/>
+        <v>5.2094861528414214</v>
+      </c>
+      <c r="H47" s="10">
+        <f t="shared" si="7"/>
+        <v>4.5849674786705723</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" si="6"/>
+        <v>0.39002357438811514</v>
+      </c>
+      <c r="M47" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" s="27">
+        <v>14</v>
+      </c>
+      <c r="O47" s="27">
+        <v>5.2839757248055319</v>
+      </c>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="27"/>
+      <c r="R47" s="27"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="20"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="20"/>
+      <c r="AA47" s="20"/>
+      <c r="AB47" s="20"/>
+    </row>
+    <row r="48" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="24">
+        <v>14</v>
+      </c>
+      <c r="C48" s="24">
+        <v>41</v>
+      </c>
+      <c r="D48" s="24">
+        <v>190</v>
+      </c>
+      <c r="E48" s="24">
+        <v>90</v>
+      </c>
+      <c r="F48" s="10">
+        <f t="shared" si="3"/>
+        <v>3.713572066704308</v>
+      </c>
+      <c r="G48" s="10">
+        <f t="shared" si="4"/>
+        <v>5.2470240721604862</v>
+      </c>
+      <c r="H48" s="10">
+        <f t="shared" si="7"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="I48" s="10">
+        <f t="shared" si="6"/>
+        <v>0.55832936230249519</v>
+      </c>
+      <c r="V48" s="20"/>
+      <c r="W48" s="20"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="20"/>
+      <c r="AA48" s="20"/>
+      <c r="AB48" s="20"/>
+    </row>
+    <row r="49" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B49" s="24">
+        <v>15</v>
+      </c>
+      <c r="C49" s="24">
+        <v>35</v>
+      </c>
+      <c r="D49" s="24">
+        <v>150</v>
+      </c>
+      <c r="E49" s="24">
+        <v>80</v>
+      </c>
+      <c r="F49" s="10">
+        <f t="shared" si="3"/>
+        <v>3.5553480614894135</v>
+      </c>
+      <c r="G49" s="10">
+        <f t="shared" si="4"/>
+        <v>5.0106352940962555</v>
+      </c>
+      <c r="H49" s="10">
+        <f t="shared" si="7"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="I49" s="10">
+        <f t="shared" si="6"/>
+        <v>0.39514884670079459</v>
+      </c>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="O49" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="P49" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q49" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="R49" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="S49" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="T49" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="U49" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
+    </row>
+    <row r="50" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M50" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="N50" s="26">
+        <v>-11.915254786513559</v>
+      </c>
+      <c r="O50" s="26">
+        <v>2.0844734713102215</v>
+      </c>
+      <c r="P50" s="26">
+        <v>-5.7161940175828088</v>
+      </c>
+      <c r="Q50" s="26">
+        <v>1.3492573151374347E-4</v>
+      </c>
+      <c r="R50" s="26">
+        <v>-16.503149963472062</v>
+      </c>
+      <c r="S50" s="26">
+        <v>-7.3273596095550584</v>
+      </c>
+      <c r="T50" s="26">
+        <v>-16.503149963472062</v>
+      </c>
+      <c r="U50" s="26">
+        <v>-7.3273596095550584</v>
+      </c>
+      <c r="V50" s="20"/>
+      <c r="W50" s="20"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="20"/>
+      <c r="AA50" s="20"/>
+      <c r="AB50" s="20"/>
+    </row>
+    <row r="51" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M51" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="N51" s="26">
+        <v>3.4162990807049711</v>
+      </c>
+      <c r="O51" s="26">
+        <v>2.3224613110340253</v>
+      </c>
+      <c r="P51" s="26">
+        <v>1.4709821276566017</v>
+      </c>
+      <c r="Q51" s="26">
+        <v>0.16931521423296181</v>
+      </c>
+      <c r="R51" s="26">
+        <v>-1.695403799767889</v>
+      </c>
+      <c r="S51" s="26">
+        <v>8.5280019611778322</v>
+      </c>
+      <c r="T51" s="26">
+        <v>-1.695403799767889</v>
+      </c>
+      <c r="U51" s="26">
+        <v>8.5280019611778322</v>
+      </c>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="20"/>
+      <c r="AA51" s="20"/>
+      <c r="AB51" s="20"/>
+    </row>
+    <row r="52" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="M52" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="N52" s="26">
+        <v>-0.39231782202371313</v>
+      </c>
+      <c r="O52" s="26">
+        <v>2.4710370841227252</v>
+      </c>
+      <c r="P52" s="26">
+        <v>-0.15876646471414449</v>
+      </c>
+      <c r="Q52" s="26">
+        <v>0.87673023120928584</v>
+      </c>
+      <c r="R52" s="26">
+        <v>-5.8310337742139451</v>
+      </c>
+      <c r="S52" s="26">
+        <v>5.0463981301665184</v>
+      </c>
+      <c r="T52" s="26">
+        <v>-5.8310337742139451</v>
+      </c>
+      <c r="U52" s="26">
+        <v>5.0463981301665184</v>
+      </c>
+      <c r="V52" s="20"/>
+      <c r="W52" s="20"/>
+      <c r="X52" s="20"/>
+      <c r="Y52" s="20"/>
+      <c r="Z52" s="20"/>
+      <c r="AA52" s="20"/>
+      <c r="AB52" s="20"/>
+    </row>
+    <row r="53" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M53" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="N53" s="27">
+        <v>-0.40999899753377794</v>
+      </c>
+      <c r="O53" s="27">
+        <v>1.3263187285936295</v>
+      </c>
+      <c r="P53" s="27">
+        <v>-0.30912554327610453</v>
+      </c>
+      <c r="Q53" s="27">
+        <v>0.76300237499119661</v>
+      </c>
+      <c r="R53" s="27">
+        <v>-3.3292068367199659</v>
+      </c>
+      <c r="S53" s="27">
+        <v>2.5092088416524096</v>
+      </c>
+      <c r="T53" s="27">
+        <v>-3.3292068367199659</v>
+      </c>
+      <c r="U53" s="27">
+        <v>2.5092088416524096</v>
+      </c>
+    </row>
+    <row r="56" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L56" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="M56" s="10">
+        <f>EXP(N50)</f>
+        <v>6.6876047219111252E-6</v>
+      </c>
+    </row>
+    <row r="57" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L57" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="M57" s="10">
+        <f>N51</f>
+        <v>3.4162990807049711</v>
+      </c>
+    </row>
+    <row r="58" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L58" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="M58" s="10">
+        <f>-2*N53/(M57*(1-M57))</f>
+        <v>-9.9335896990041667E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -6211,7 +10713,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="A7B9363F-F50B-4844-AC26-224D7B9B3BA5">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95BEC90-C6E3-4290-9EA0-34377F5FDF3C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>
